--- a/selenium-tests/Hospital_Qswift_Login_E2E_Test_Report.xlsx
+++ b/selenium-tests/Hospital_Qswift_Login_E2E_Test_Report.xlsx
@@ -62,7 +62,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>28/10/2026, 8:40:10 pm</t>
+    <t>28/10/2026, 11:42:36 pm</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>

--- a/selenium-tests/Hospital_Qswift_Login_E2E_Test_Report.xlsx
+++ b/selenium-tests/Hospital_Qswift_Login_E2E_Test_Report.xlsx
@@ -62,7 +62,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>28/10/2026, 11:42:36 pm</t>
+    <t>29/10/2026, 12:03:41 am</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>

--- a/selenium-tests/Hospital_Qswift_Login_E2E_Test_Report.xlsx
+++ b/selenium-tests/Hospital_Qswift_Login_E2E_Test_Report.xlsx
@@ -62,7 +62,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>29/10/2026, 12:03:41 am</t>
+    <t>29/10/2026, 12:06:49 am</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>
